--- a/artfynd/A 17288-2024 artfynd.xlsx
+++ b/artfynd/A 17288-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117806677</v>
+        <v>117806692</v>
       </c>
       <c r="B2" t="n">
-        <v>97815</v>
+        <v>100097</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223609</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine subsp. helleborine</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -767,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Växte mellan 3 st barkborreangripna döda granar.</t>
+          <t>Finns här och där l berget.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117806692</v>
+        <v>117806677</v>
       </c>
       <c r="B3" t="n">
-        <v>100097</v>
+        <v>97815</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,26 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>223609</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Finns här och där l berget.</t>
+          <t>Växte mellan 3 st barkborreangripna döda granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 17288-2024 artfynd.xlsx
+++ b/artfynd/A 17288-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117806692</v>
       </c>
       <c r="B2" t="n">
-        <v>100097</v>
+        <v>100099</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>117806677</v>
       </c>
       <c r="B3" t="n">
-        <v>97815</v>
+        <v>97817</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
